--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="500">
   <si>
     <t>Filename</t>
   </si>
@@ -808,703 +808,712 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9947,0.0004,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0188,0.0026,0.0014,0.9905</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9818,0.0022,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9796,0.0011,0.0001,0.0078</t>
+  </si>
+  <si>
+    <t>0.1974,0.0015,0.0001,0.8753</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0006,0.0000,0.0001</t>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9159,0.0009,0.0865,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0017,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0598,0.0007,0.9552,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.9500,0.0001,0.0845,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9979,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9524,0.0006,0.0345,0.0003</t>
+  </si>
+  <si>
+    <t>0.9153,0.0016,0.0715,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.0004,0.9932,0.0023</t>
+  </si>
+  <si>
+    <t>0.0195,0.0000,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.9417,0.0007,0.0601,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9993,0.0012</t>
+  </si>
+  <si>
+    <t>0.0326,0.9802,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.7691,0.1837,0.0076,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0054,0.9984,0.0032</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9614,0.0016,0.0314,0.0003</t>
+  </si>
+  <si>
+    <t>0.0612,0.0002,0.9589,0.0007</t>
+  </si>
+  <si>
+    <t>0.0790,0.9315,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0066,0.0000</t>
+  </si>
+  <si>
+    <t>0.0924,0.6002,0.0161,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.0008,0.9927,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.4444,0.9293,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9983,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.0224,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.2790,0.1478,0.0030,0.3335</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3809,0.9938,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0646,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0414,0.9965,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0010,0.9993,0.0013</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0189,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0020,0.9974,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0345,0.9735,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0002,0.0170,0.0000</t>
+  </si>
+  <si>
+    <t>0.8564,0.0092,0.0829,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0013,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9841,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.6479,0.9706,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.6725,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0021,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0034,0.0004,0.0011,0.9972</t>
+  </si>
+  <si>
+    <t>0.0043,0.0002,0.0005,0.9975</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.0978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9660,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7320,0.9249,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9114,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9820,0.0334,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0153,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0679,0.0035,0.9228,0.0002</t>
+  </si>
+  <si>
+    <t>0.9285,0.0000,0.0549,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.0005,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9986,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.2402,0.8348,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0177,0.0084,0.9567,0.0019</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1610,0.4213,0.0597,0.0083</t>
+  </si>
+  <si>
+    <t>0.0830,0.0039,0.8463,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.1629,0.0007,0.9898</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.1760,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1103,0.8168,0.0336,0.0001</t>
+  </si>
+  <si>
+    <t>0.6881,0.3770,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0003,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.8375,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6915,0.9945,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.0013,0.9919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0081,0.9879,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0000,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.4001,0.0004,0.6498,0.0002</t>
+  </si>
+  <si>
+    <t>0.3845,0.0001,0.7612,0.0001</t>
+  </si>
+  <si>
+    <t>0.9822,0.0001,0.0099,0.0001</t>
+  </si>
+  <si>
+    <t>0.0612,0.0002,0.0003,0.9766</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9876,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9332,0.0830,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9786,0.0002,0.0029,0.0092</t>
+  </si>
+  <si>
+    <t>0.0004,0.0052,0.9971,0.0119</t>
+  </si>
+  <si>
+    <t>0.9195,0.0000,0.0515,0.0017</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2245,0.8541,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0018,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0066,0.0067,0.0001</t>
+  </si>
+  <si>
+    <t>0.0449,0.1912,0.5447,0.0001</t>
+  </si>
+  <si>
+    <t>0.9923,0.0018,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.9918,0.0056,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9485,0.0164,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9467,0.0471,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9795,0.0251,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0111,0.9991,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0046,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0013,0.0017,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0023,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9509,0.0569,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9928,0.0045,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0502,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0090,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0015,0.9938,0.0010</t>
+  </si>
+  <si>
+    <t>0.0056,0.0006,0.9915,0.0003</t>
+  </si>
+  <si>
+    <t>0.7785,0.0510,0.0581,0.0002</t>
+  </si>
+  <si>
+    <t>0.0582,0.0058,0.9365,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.2105,0.9012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8102,0.0204,0.0590,0.0002</t>
+  </si>
+  <si>
+    <t>0.7782,0.0009,0.2172,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0011,0.9925,0.0012</t>
+  </si>
+  <si>
+    <t>0.0021,0.9969,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9983,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.6504,0.5290,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0281,0.9769,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.9956,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.4218,0.4287,0.0071,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0000,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.9919,0.0013,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0157,0.0097,0.9691,0.0010</t>
+  </si>
+  <si>
+    <t>0.0463,0.0085,0.8957,0.0047</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9989,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.0466,0.9894,0.0067</t>
+  </si>
+  <si>
+    <t>0.0183,0.0497,0.9577,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.3825,0.7482,0.0029</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0034,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0013,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9845,0.0155,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0063,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0023,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8281,0.0004,0.1850,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0007,0.9967,0.0003</t>
-  </si>
-  <si>
-    <t>0.9371,0.0003,0.0994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0049,0.0019,0.9916,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0003,0.0121,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0092,0.9920,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9988,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.1136,0.0009,0.8751,0.0005</t>
-  </si>
-  <si>
-    <t>0.4660,0.0008,0.3756,0.0048</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0004,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0000,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0315,0.0008,0.9682,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9988,0.0011</t>
-  </si>
-  <si>
-    <t>0.6070,0.4218,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.1401,0.8610,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0012,0.9990,0.0030</t>
-  </si>
-  <si>
-    <t>0.0007,0.9993,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9673,0.0006,0.0303,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0005,0.0198,0.0001</t>
-  </si>
-  <si>
-    <t>0.7721,0.2636,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9230,0.1256,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0107,0.9965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0102,0.0001,0.9812,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.0308,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0022,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9657,0.0001,0.8779</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0153,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0609,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.0001,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.2960,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.9982,0.0087</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9776,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0081,0.9978,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0013,0.9970,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9900,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.9965,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9460,0.0002,0.0876,0.0000</t>
-  </si>
-  <si>
-    <t>0.9857,0.0018,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0008,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9932,0.7190,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.5389,0.9823,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.7950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0082,0.9985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.0009,0.9990</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.1811,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9819,0.9922,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9737,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8520,0.9942,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.7593,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9816,0.0349,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0012,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9917,0.0081,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0008</t>
-  </si>
-  <si>
-    <t>0.0035,0.0015,0.9924,0.0006</t>
-  </si>
-  <si>
-    <t>0.5697,0.0001,0.2838,0.0072</t>
-  </si>
-  <si>
-    <t>0.0045,0.0001,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.9891,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0798,0.9446,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.8754,0.0063,0.0748,0.0001</t>
-  </si>
-  <si>
-    <t>0.9898,0.0002,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0255,0.7438,0.0570,0.0203</t>
-  </si>
-  <si>
-    <t>0.9224,0.0019,0.0556,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0203,0.0008,0.9960</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9838,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1793,0.8607,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.8895,0.1122,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0018,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.8942,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0144,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0010,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0014,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.9915,0.0002,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.8425,0.0032,0.1055,0.0007</t>
-  </si>
-  <si>
-    <t>0.0633,0.0001,0.9537,0.0003</t>
-  </si>
-  <si>
-    <t>0.9849,0.0000,0.0197,0.0000</t>
-  </si>
-  <si>
-    <t>0.1086,0.0001,0.0004,0.9500</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.8273,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.0172,0.9743,0.0052,0.0009</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9798,0.0006,0.0025,0.0138</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9995,0.0025</t>
-  </si>
-  <si>
-    <t>0.9812,0.0000,0.0120,0.0007</t>
-  </si>
-  <si>
-    <t>0.0136,0.9395,0.0783,0.0007</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8463,0.0120,0.0930,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0012,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0034,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0012,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9503,0.0427,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.2558,0.7404,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.9770,0.0253,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0366,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0025,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9651,0.0313,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9337,0.0216,0.0225,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0700,0.9990,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0014,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0017,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.5533,0.0038,0.3635,0.0010</t>
-  </si>
-  <si>
-    <t>0.4852,0.0461,0.2448,0.0002</t>
-  </si>
-  <si>
-    <t>0.0185,0.0145,0.9660,0.0001</t>
-  </si>
-  <si>
-    <t>0.0244,0.0074,0.9628,0.0000</t>
-  </si>
-  <si>
-    <t>0.9368,0.0023,0.0594,0.0000</t>
-  </si>
-  <si>
-    <t>0.8184,0.0002,0.2067,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.0015,0.9890,0.0005</t>
-  </si>
-  <si>
-    <t>0.0054,0.9961,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0618,0.9670,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9155,0.1864,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1660,0.8759,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.9950,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8963,0.0641,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9745,0.0013,0.0042,0.0022</t>
-  </si>
-  <si>
-    <t>0.3622,0.0021,0.5454,0.0026</t>
-  </si>
-  <si>
-    <t>0.0274,0.0015,0.9723,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9981,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.9955,0.0013</t>
-  </si>
-  <si>
-    <t>0.0207,0.0908,0.9487,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.2326,0.8761,0.0041</t>
-  </si>
-  <si>
-    <t>0.9953,0.0030,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9893,0.0100,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0034,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0022,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9996,0.0012</t>
-  </si>
-  <si>
-    <t>0.0665,0.5654,0.0963,0.0015</t>
-  </si>
-  <si>
-    <t>0.9962,0.0005,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.0000,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0015,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.2266,0.9550,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.0015,0.9889,0.0001</t>
+    <t>0.0000,0.0003,1.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.1307,0.6001,0.0615,0.0004</t>
+  </si>
+  <si>
+    <t>0.9864,0.0012,0.0052,0.0010</t>
+  </si>
+  <si>
+    <t>0.0161,0.0000,0.9911,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0071,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.3048,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0002,0.9953,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0002,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9981,0.0006</t>
-  </si>
-  <si>
-    <t>0.9456,0.0009,0.0394,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9915,0.0101,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0032,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0048,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0187,0.0060,0.9678,0.0002</t>
-  </si>
-  <si>
-    <t>0.0219,0.0001,0.9792,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.0011,0.9772,0.0307</t>
-  </si>
-  <si>
-    <t>0.0057,0.0086,0.9836,0.0026</t>
-  </si>
-  <si>
-    <t>0.2618,0.0015,0.6847,0.0019</t>
-  </si>
-  <si>
-    <t>0.9647,0.0000,0.0002,0.0339</t>
-  </si>
-  <si>
-    <t>0.0000,0.0361,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0504,0.0001,0.0012,0.9758</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9869,0.0001,0.0003,0.0061</t>
+    <t>0.0000,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.3129,0.9922,0.0004</t>
+  </si>
+  <si>
+    <t>0.9067,0.0023,0.0308,0.0032</t>
+  </si>
+  <si>
+    <t>0.9616,0.0001,0.0538,0.0001</t>
+  </si>
+  <si>
+    <t>0.9782,0.0005,0.0107,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0079,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0270,0.0145,0.9506,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0037,0.9911,0.0095</t>
+  </si>
+  <si>
+    <t>0.0309,0.0004,0.9611,0.0006</t>
+  </si>
+  <si>
+    <t>0.0051,0.0003,0.9904,0.0010</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0031,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0057,0.0000,0.0005,0.9972</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0002,0.0004,0.0021</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1899,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1904,7 +1913,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1918,7 +1927,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1932,7 +1941,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1946,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1960,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1974,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1988,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2030,7 +2039,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2044,7 +2053,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,7 +2067,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2072,7 +2081,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,10 +2092,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2100,7 +2109,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2114,7 +2123,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2128,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2142,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,7 +2165,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2170,7 +2179,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2184,7 +2193,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,10 +2204,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,7 +2221,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2226,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2240,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2254,7 +2263,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,10 +2274,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2282,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,10 +2302,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,10 +2316,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2324,7 +2333,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2338,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2352,7 +2361,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2363,10 +2372,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2377,10 +2386,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2394,7 +2403,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,7 +2417,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2422,7 +2431,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2436,7 +2445,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2450,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,7 +2473,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2478,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2492,7 +2501,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,7 +2515,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2520,7 +2529,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2534,7 +2543,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2548,7 +2557,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2562,7 +2571,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2576,7 +2585,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2590,7 +2599,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2604,7 +2613,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2618,7 +2627,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2632,7 +2641,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2646,7 +2655,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2660,7 +2669,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2674,7 +2683,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2688,7 +2697,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2702,7 +2711,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2716,7 +2725,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2730,7 +2739,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2744,7 +2753,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2758,7 +2767,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2772,7 +2781,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2786,7 +2795,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2800,7 +2809,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2814,7 +2823,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2828,7 +2837,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,7 +2851,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2856,7 +2865,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2870,7 +2879,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,7 +2893,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2898,7 +2907,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,7 +2921,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3108,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3122,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3136,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3150,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3164,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3178,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3192,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3206,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3220,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3234,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3248,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3262,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3276,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3290,7 +3299,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3304,7 +3313,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3318,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3332,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3346,7 +3355,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,7 +3369,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3374,7 +3383,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3388,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3402,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3416,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3430,7 +3439,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3444,7 +3453,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3458,7 +3467,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,7 +3481,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,10 +3492,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,7 +3509,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,10 +3520,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,10 +3534,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3542,7 +3551,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3556,7 +3565,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3570,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3584,7 +3593,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3598,7 +3607,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3612,7 +3621,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,7 +3635,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,7 +3649,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3654,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3668,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3682,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3696,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3710,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3724,7 +3733,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>272</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3777,7 +3786,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>386</v>
@@ -3833,7 +3842,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>390</v>
@@ -3892,7 +3901,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3906,7 +3915,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3920,7 +3929,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3934,7 +3943,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3948,7 +3957,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3962,7 +3971,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3976,7 +3985,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,10 +3996,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4004,7 +4013,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4018,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4032,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4046,7 +4055,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4060,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4074,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4088,7 +4097,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4102,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4116,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,10 +4136,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4144,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4158,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4172,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4186,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4200,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4214,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4228,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4242,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4256,7 +4265,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4270,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,7 +4293,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4295,10 +4304,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4312,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4326,7 +4335,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4340,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4354,7 +4363,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4368,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,7 +4391,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4396,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4410,7 +4419,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4424,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4438,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4452,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4480,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4494,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4508,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4522,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,10 +4542,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4550,7 +4559,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,7 +4573,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4578,7 +4587,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4592,7 +4601,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4606,7 +4615,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,7 +4629,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,7 +4643,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4648,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,10 +4668,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,7 +4685,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4690,7 +4699,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4701,10 +4710,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4718,7 +4727,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4732,7 +4741,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4746,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4760,7 +4769,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4774,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4788,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4802,7 +4811,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4816,7 +4825,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,7 +4839,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4844,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4858,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4872,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4886,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4900,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4914,7 +4923,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4928,7 +4937,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4942,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>414</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4956,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,7 +4979,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4984,7 +4993,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4998,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5012,7 +5021,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5026,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5040,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5054,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5068,7 +5077,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5082,7 +5091,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5096,7 +5105,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5110,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5138,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5152,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5166,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5180,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>274</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5194,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5208,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5222,7 +5231,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5236,7 +5245,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5250,7 +5259,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5264,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5292,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5306,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5320,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5334,7 +5343,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5348,7 +5357,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5362,7 +5371,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5376,7 +5385,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5390,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5404,7 +5413,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5418,7 +5427,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>495</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5432,7 +5441,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,7 +5455,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
